--- a/examples/enset/modele-u1.xlsx
+++ b/examples/enset/modele-u1.xlsx
@@ -667,19 +667,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
     <col width="32" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
     <col width="32" customWidth="1" min="13" max="13"/>
@@ -690,20 +690,21 @@
     <col width="32" customWidth="1" min="18" max="18"/>
     <col width="32" customWidth="1" min="19" max="19"/>
     <col width="32" customWidth="1" min="20" max="20"/>
-    <col width="31" customWidth="1" min="21" max="21"/>
-    <col width="32" customWidth="1" min="22" max="22"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="31" customWidth="1" min="22" max="22"/>
     <col width="32" customWidth="1" min="23" max="23"/>
     <col width="32" customWidth="1" min="24" max="24"/>
-    <col width="23" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
-    <col width="30" customWidth="1" min="27" max="27"/>
-    <col width="32" customWidth="1" min="28" max="28"/>
+    <col width="32" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
     <col width="32" customWidth="1" min="29" max="29"/>
     <col width="32" customWidth="1" min="30" max="30"/>
-    <col width="27" customWidth="1" min="31" max="31"/>
-    <col width="24" customWidth="1" min="32" max="32"/>
-    <col width="20" customWidth="1" min="33" max="33"/>
-    <col width="19" customWidth="1" min="34" max="34"/>
+    <col width="32" customWidth="1" min="31" max="31"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="24" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="19" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -714,165 +715,170 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>nom_prenom</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>population</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>departement</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pays_destination</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>duree_jours</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>rang_scientifique</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>penalite_beneficies_3ans (n manuel)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>prix_distinctions (Oui/Non)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>projet_international.projet_intl (qte)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>projet_national.projet_national (qte)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>encadrement_arrete_1275.projet_1275 (qte)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>encadrement_projet_labelise (Oui/Non)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>cours_tronc_commun.cours_tc (qte)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>expertise_reviewing.revue_a_plus (qte)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>expertise_reviewing.revue_a (qte)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>expertise_reviewing.revue_b (qte)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>expertise_reviewing.revue_c (qte)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>structures_accompagnement.attestation (qte)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>citations_scopus.citation (qte)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>citations_scopus (url profil)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>polycopie_pedagogique (Oui/Non)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>polycopie_pedagogique (bonus 1 Oui/Non)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>polycopie_pedagogique (bonus 2 Oui/Non)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>chapterbook (Oui/Non)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>livre_isbn (Oui/Non)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>livre_isbn (bonus 1 Oui/Non)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>responsabilites_scientifiques.membre_conseil (qte)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>responsabilites_scientifiques.president_instance (qte)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>responsabilites_scientifiques.editeur (qte)</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>poste_superieur (Oui/Non)</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>montant_indemnite (DA)</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>billet_estime (DA)</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>frais_divers (DA)</t>
         </is>
@@ -880,22 +886,19 @@
     </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$E$2:$E$7</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$C$2:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=Listes!$C$2:$C$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="V2:V500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -913,7 +916,10 @@
     <dataValidation sqref="AA2:AA500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$C$2:$C$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AE2:AE500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AB2:AB500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>=Listes!$C$2:$C$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AF2:AF500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Listes!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/examples/enset/modele-u1.xlsx
+++ b/examples/enset/modele-u1.xlsx
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Citations Scopus de l'établissement (nombre depuis le dernier bénéfice + URL du profil Scopus / Google Scholar — https://www.scopus.com/freelookup/form/author.uri)</t>
+          <t>Citations Scopus de l'établissement (nombre depuis le dernier bénéfice)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
